--- a/frontend/public/b2c-order-upload-template.xlsx
+++ b/frontend/public/b2c-order-upload-template.xlsx
@@ -26,6 +26,9 @@
     <x:t>차수</x:t>
   </x:si>
   <x:si>
+    <x:t>오더번호</x:t>
+  </x:si>
+  <x:si>
     <x:t>바코드</x:t>
   </x:si>
   <x:si>
@@ -41,12 +44,24 @@
     <x:t>1</x:t>
   </x:si>
   <x:si>
+    <x:t>ORD-0001</x:t>
+  </x:si>
+  <x:si>
     <x:t>BC-0001</x:t>
   </x:si>
   <x:si>
     <x:t>BC-0002</x:t>
   </x:si>
   <x:si>
+    <x:t>ORD-0002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BC-0003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
     <x:t>컬럼</x:t>
   </x:si>
   <x:si>
@@ -68,16 +83,22 @@
     <x:t>차수(wave). 비우면 1. 1~9999 정수.</x:t>
   </x:si>
   <x:si>
-    <x:t>바코드 = 오더번호. 영문·숫자·하이픈(-)·언더스코어(_) 1~100자. 같은 배치 안에서 유일해야 함.</x:t>
+    <x:t>오더번호 = wcs_order.order_no. 영문·숫자·하이픈(-)·언더스코어(_) 1~100자. 같은 배치 안에서 같은 오더번호 행들은 하나의 오더로 묶임(1 오더:N 바코드).</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바코드 = order_item.barcode. 영문·숫자·하이픈(-)·언더스코어(_) 1~100자. 같은 배치 안에서 유일해야 함(오더번호와는 별개 값).</x:t>
   </x:si>
   <x:si>
     <x:t>계획수량(order_item.planned_qty). 비우면 1. 1~9999 정수.</x:t>
   </x:si>
   <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
     <x:t>안내</x:t>
   </x:si>
   <x:si>
-    <x:t>· 한 행 = 오더/바코드 1건. 첫 행(헤더)은 수정하지 마세요.</x:t>
+    <x:t>· 한 오더에 여러 바코드를 넣을 수 있습니다: 같은 오더번호를 여러 행에 반복하고 각 행에 서로 다른 바코드를 적으세요(예시 시트 ORD-0001 참고). 첫 행(헤더)은 수정하지 마세요.</x:t>
   </x:si>
   <x:si>
     <x:t>· 업로드된 오더는 목적지 미할당 상태로 추가됩니다(목적지·셀 배정은 설비 관리에서 수행).</x:t>
@@ -86,7 +107,7 @@
     <x:t>· 한 행이라도 오류가 있으면 전체가 취소됩니다(부분 반영 없음). 같은 데이터 재업로드는 중복 생성되지 않습니다(멱등).</x:t>
   </x:si>
   <x:si>
-    <x:t>· 한 번에 최대 1000행까지 업로드할 수 있습니다.</x:t>
+    <x:t>· 배치 안에서 바코드는 유일해야 합니다. 한 번에 최대 1000행까지 업로드할 수 있습니다.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -126,7 +147,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="2">
     <x:border diagonalUp="0" diagonalDown="0">
       <x:left style="none">
         <x:color rgb="FF000000"/>
@@ -138,6 +159,23 @@
         <x:color rgb="FF000000"/>
       </x:top>
       <x:bottom style="none">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
       <x:diagonal style="none">
@@ -145,14 +183,17 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -161,15 +202,15 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -468,17 +509,17 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E3"/>
+  <x:dimension ref="A1:F4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="14.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="16.710625" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="8.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18.710625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="8.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="5" width="16.710625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:5">
+    <x:row r="1" spans="1:6">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -494,39 +535,68 @@
       <x:c r="E1" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:5">
+      <x:c r="F1" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:6">
       <x:c r="A2" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:6">
+      <x:c r="A3" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="B3" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="C3" s="0" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:5">
-      <x:c r="A3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:6">
+      <x:c r="A4" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>7</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -543,23 +613,23 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C12"/>
+  <x:dimension ref="A1:C13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="8.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="80.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="90.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:3">
-      <x:c r="A1" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>12</x:v>
+    <x:row r="1" spans="1:3" s="2" customFormat="1">
+      <x:c r="A1" s="3" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C1" s="3" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
@@ -567,10 +637,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -578,10 +648,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
@@ -589,10 +659,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
@@ -600,10 +670,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
@@ -611,35 +681,57 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:3">
+      <x:c r="A7" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
-      <x:c r="A8" s="3" t="s">
-        <x:v>19</x:v>
+      <x:c r="A8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
-      <x:c r="A9" s="0" t="s">
-        <x:v>20</x:v>
+      <x:c r="A9" s="2" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:3">
+      <x:c r="A13" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
